--- a/SaidaRPA/Excel/tmr-distribuidora-indicador_01-01-2026_31-01-2026.xlsx
+++ b/SaidaRPA/Excel/tmr-distribuidora-indicador_01-01-2026_31-01-2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,10 +454,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risco a Imagem</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>520.78</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -467,15 +469,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tratativas detratores</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Fila INS Cliente</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>337.74</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CEA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -484,37 +488,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>520.78</v>
+        <v>483.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CEEE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fila INS Cliente</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>337.74</v>
+        <v>164.93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CEA</t>
+          <t>CEEE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>483.82</v>
+        <v>143.13</v>
       </c>
     </row>
     <row r="8">
@@ -525,17 +529,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tratativas detratores</t>
+          <t>Imprensa | Favorabilidade</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5541.47</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEEE</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -544,28 +548,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>164.93</v>
+        <v>1162.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEEE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fila INS Cliente</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>119.61</v>
+        <v>204.76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEEE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -574,28 +578,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16.95</v>
+        <v>37.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEEE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rechamadas</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.72</v>
+        <v>31.35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -604,28 +608,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1162.41</v>
+        <v>209.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tratativas detratores</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20108.69</v>
+        <v>161.66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -633,29 +637,25 @@
           <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>204.76</v>
-      </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Imprensa | Favorabilidade</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>37.33</v>
-      </c>
+          <t>Redes Sociais | Menções Negativas</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -664,159 +664,36 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>31.35</v>
+        <v>160.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tratativas detratores</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>616.4299999999999</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Comportamento Inadequado</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>209.16</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
           <t>Fila INS Cliente</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>161.66</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Redes Sociais | Menções Negativas</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Tratativas detratores</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Fila INS Cliente</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>160.09</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Tratativas detratores</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>616.4299999999999</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Fila INS Cliente</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
+      <c r="C19" t="n">
         <v>100.9</v>
       </c>
     </row>
